--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -672,37 +672,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 148127억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 148130억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 154336억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 154473억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159907억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 160175억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 161176억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 161808억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 160304억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 161061억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 158427억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 159178억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -936,13 +936,13 @@
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 567억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 568억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 624억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 625억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1791,37 +1791,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 148127억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 148130억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 154336억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 154473억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159907억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 160175억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 161176억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 161808억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 160304억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 161061억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 158427억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 159178억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2270,13 +2270,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 567억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 568억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 624억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 625억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6571,20 +6571,20 @@
         <v>0.188238</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.207975</v>
+        <v>0.209014</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.200388</v>
+        <v>0.20241</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.151706</v>
+        <v>0.156239</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.082203</v>
+        <v>0.087311</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.026495</v>
+        <v>0.030471</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6720,23 +6720,23 @@
         <v>0.168329</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.168332</v>
+        <v>0.168319</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.168311</v>
+        <v>0.168337</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.168334</v>
+        <v>0.168318</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.168324</v>
+        <v>0.168316</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.168337</v>
+        <v>0.168313</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6875,23 +6875,23 @@
         <v>0.185292</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185267</v>
+        <v>0.185273</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185293</v>
+        <v>0.185291</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185291</v>
+        <v>0.18529</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185291</v>
+        <v>0.185288</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185287</v>
+        <v>0.185279</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7156,7 +7156,7 @@
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="AL25" s="29" t="n">
         <v>6.82</v>
@@ -7459,23 +7459,23 @@
         <v>0.197774</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.197871</v>
+        <v>0.197873</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
+        <v>0.197848</v>
+      </c>
+      <c r="AL27" s="24" t="n">
+        <v>0.197837</v>
+      </c>
+      <c r="AM27" s="24" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="AN27" s="24" t="n">
         <v>0.197811</v>
-      </c>
-      <c r="AL27" s="24" t="n">
-        <v>0.19775</v>
-      </c>
-      <c r="AM27" s="24" t="n">
-        <v>0.197766</v>
-      </c>
-      <c r="AN27" s="24" t="n">
-        <v>0.197737</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7621,16 +7621,16 @@
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
+        <v>0.999794</v>
+      </c>
+      <c r="AL28" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AL28" s="24" t="n">
-        <v>0.999835</v>
-      </c>
       <c r="AM28" s="24" t="n">
-        <v>0.999824</v>
+        <v>1</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.9998010000000001</v>
+        <v>1</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7839,23 +7839,23 @@
       <c r="AF30" s="31" t="n"/>
       <c r="AG30" s="31" t="n"/>
       <c r="AH30" s="24" t="n">
-        <v>0.185221</v>
+        <v>0.185413</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>0.204324</v>
+        <v>0.205384</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>0.196675</v>
+        <v>0.198644</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>0.149802</v>
+        <v>0.154101</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>0.081134</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>0.026223</v>
+        <v>0.030069</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8111,7 +8111,7 @@
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8223,10 +8223,10 @@
         <v>302.01</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
@@ -8239,7 +8239,7 @@
         <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8567,23 +8567,23 @@
         <v>-0.273977</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.08115799999999999</v>
+        <v>0.081173</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07001300000000001</v>
+        <v>0.07005400000000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.06363000000000001</v>
+        <v>0.063732</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.2985</v>
+        <v>-0.298196</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.100033</v>
+        <v>0.100416</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.080681</v>
+        <v>0.08097500000000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9228,20 +9228,20 @@
         <v>0.028771</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.042052</v>
+        <v>-0.042893</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.107605</v>
+        <v>-0.108414</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.128163</v>
+        <v>-0.12898</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.109322</v>
+        <v>-0.111864</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.07989499999999999</v>
+        <v>-0.081722</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9651,23 +9651,23 @@
         <v>0.185292</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.185267</v>
+        <v>0.185273</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.185293</v>
+        <v>0.185291</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.185291</v>
+        <v>0.18529</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.185291</v>
+        <v>0.185288</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.185287</v>
+        <v>0.185279</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -678,31 +678,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 154473억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155164억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 160175억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 163451억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 161808억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 170488억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 161061억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 178618억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159178억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 188776억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -924,25 +924,25 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 760억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 761억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 809억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 810억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 568억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 572억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 625억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 635억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1797,31 +1797,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 154473억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155164억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 160175억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 163451억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 161808억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 170488억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 161061억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 178618억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159178억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 188776억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2258,25 +2258,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 760억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 761억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 809억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 810억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 568억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 572억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 625억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 635억 × 3.37% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4379,7 +4379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 58.0, "op_wape_pct": 35.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 198.49, "rev_act": 307.62, "op_pred": 27.56, "op_act": 61.99}, {"q": "2025Q4", "rev_pred": 207.81, "rev_act": 207.13, "op_pred": 28.85, "op_act": 40.45}, {"q": "2026Q1", "rev_pred": 509.71, "rev_act": 259.36, "op_pred": 70.77, "op_act": 80.42}, {"q": "2026Q2", "rev_pred": 467.55, "rev_act": 239.53, "op_pred": 64.92, "op_act": 41.99}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 58.0, "op_wape_pct": 35.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 198.49, "rev_act": 307.62, "op_pred": 27.56, "op_act": 61.99}, {"q": "2025Q4", "rev_pred": 207.81, "rev_act": 207.13, "op_pred": 28.85, "op_act": 40.45}, {"q": "2026Q1", "rev_pred": 509.71, "rev_act": 259.36, "op_pred": 70.77, "op_act": 80.42}, {"q": "2026Q2", "rev_pred": 467.55, "rev_act": 239.53, "op_pred": 64.92, "op_act": 41.99}]}</t>
         </is>
       </c>
     </row>
@@ -6571,20 +6571,20 @@
         <v>0.188238</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.209014</v>
+        <v>0.214448</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.20241</v>
+        <v>0.227004</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.156239</v>
+        <v>0.218244</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.087311</v>
+        <v>0.205843</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.030471</v>
+        <v>0.216622</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6720,23 +6720,23 @@
         <v>0.168329</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.168319</v>
+        <v>0.168323</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.168337</v>
+        <v>0.168326</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.168318</v>
+        <v>0.168315</v>
       </c>
       <c r="AM22" s="24" t="n">
+        <v>0.168335</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.168316</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.168313</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6875,23 +6875,23 @@
         <v>0.185292</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185273</v>
+        <v>0.1853</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185291</v>
+        <v>0.185276</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.18529</v>
+        <v>0.185289</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185288</v>
+        <v>0.185277</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185279</v>
+        <v>0.185272</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7159,13 +7159,13 @@
         <v>6.42</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>5.27</v>
+        <v>5.35</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7459,23 +7459,23 @@
         <v>0.197774</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.197873</v>
+        <v>0.197721</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.197848</v>
+        <v>0.197854</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.197837</v>
+        <v>0.197787</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.19772</v>
+        <v>0.197778</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.197811</v>
+        <v>0.19778</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7614,23 +7614,23 @@
         <v>0.999813</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.999794</v>
+        <v>1</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>1</v>
+        <v>0.999843</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>1</v>
+        <v>0.999841</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>1</v>
+        <v>0.999831</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7842,20 +7842,20 @@
         <v>0.185413</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>0.205384</v>
+        <v>0.210682</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>0.198644</v>
+        <v>0.222927</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>0.154101</v>
+        <v>0.215443</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>0.08613999999999999</v>
+        <v>0.203044</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>0.030069</v>
+        <v>0.213585</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8098,20 +8098,20 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>302.01</v>
       </c>
       <c r="AM32" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AN32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8226,11 +8226,11 @@
         <v>-0.01</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AL33" s="29" t="n">
         <v>302.01</v>
@@ -8239,7 +8239,7 @@
         <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8570,20 +8570,20 @@
         <v>0.081173</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07005400000000001</v>
+        <v>0.070336</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.063732</v>
+        <v>0.064872</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.298196</v>
+        <v>-0.294119</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.100416</v>
+        <v>0.1099</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.08097500000000001</v>
+        <v>0.093392</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9228,20 +9228,20 @@
         <v>0.028771</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.042893</v>
+        <v>-0.043734</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.108414</v>
+        <v>-0.113269</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.12898</v>
+        <v>-0.146122</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.111864</v>
+        <v>-0.15</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.081722</v>
+        <v>-0.153034</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9351,16 +9351,16 @@
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>0.089005</v>
+        <v>0.08377</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.107884</v>
+        <v>0.09958500000000001</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.09649099999999999</v>
+        <v>0.083333</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.092166</v>
+        <v>0.069124</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -9651,23 +9651,23 @@
         <v>0.185292</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.185273</v>
+        <v>0.1853</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.185291</v>
+        <v>0.185276</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.18529</v>
+        <v>0.185289</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.185288</v>
+        <v>0.185277</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.185279</v>
+        <v>0.185272</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 152579억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 152564억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159082억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 159050억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164315억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164267억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171412억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171348억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181545억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181480억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 152579억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 152564억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159082억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 159050억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164315억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164267억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171412억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171348억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181545억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181480억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>43350</v>
+        <v>43050</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>39600</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>42900</v>
+        <v>42850</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43675</v>
+        <v>43466.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6309,20 +6309,20 @@
         <v>0.1819167</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.194190275</v>
+        <v>0.194110361</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.194197994</v>
+        <v>0.193950398</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.174154687</v>
+        <v>0.173813146</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.163391302</v>
+        <v>0.162932852</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.189881888</v>
+        <v>0.189526518</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185274611</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185297956</v>
+        <v>0.185276895</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185286292</v>
+        <v>0.185290153</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.18529194</v>
+        <v>0.185292951</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185288323</v>
+        <v>0.185282523</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185282043</v>
+        <v>0.185293538</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003880731</v>
+        <v>-0.003986799</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.005450904</v>
+        <v>0.005360371</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.002043718</v>
+        <v>0.001959121</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>302.000460844</v>
+        <v>302.000337721</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.003260917</v>
+        <v>0.003124256</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.006049596</v>
+        <v>-0.002092481</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005755388</v>
+        <v>0.006109544</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.013458054</v>
+        <v>302.007189902</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.005611524</v>
+        <v>0.001172659</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-9.0268e-05</v>
+        <v>0.003371684</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.001514882</v>
+        <v>0.000507115</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002128015</v>
+        <v>0.001206204</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.001210593</v>
+        <v>-0.002109312</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.016264254</v>
+        <v>302.015091283</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.000863695</v>
+        <v>-0.002032197</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.002222856</v>
+        <v>0.003124236</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.010501075</v>
+        <v>0.001430277</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.018664276</v>
+        <v>302.021198443</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.000916165</v>
+        <v>-0.004694966</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.005470987</v>
+        <v>0.007824104</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8156,16 +8156,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.06389001699999999</v>
+        <v>0.06387691199999999</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.29532632</v>
+        <v>-0.295354596</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.106653381</v>
+        <v>0.10662401</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.091146039</v>
+        <v>0.091121643</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>43350</v>
+        <v>43050</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1977893671674321</v>
+        <v>0.1977921026407574</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683229853462251</v>
+        <v>0.1683227007507426</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999223723024376</v>
+        <v>0.9999029521942507</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03404423284940358</v>
+        <v>0.03404456940860105</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37748,7 +37748,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39888,7 +39888,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="32">
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 152564억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 152552억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159050억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 159017억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164267억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164214억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171348억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171275억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181480억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181401억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 152564억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 152552억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159050억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 159017억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164267억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164214억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171348억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171275억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181480억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181401억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>43050</v>
+        <v>43100</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>39600</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>42850</v>
+        <v>42500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43466.7</v>
+        <v>43400</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6309,20 +6309,20 @@
         <v>0.1819167</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.194110361</v>
+        <v>0.19399049</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.193950398</v>
+        <v>0.193702802</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.173813146</v>
+        <v>0.173409507</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.162932852</v>
+        <v>0.16244384</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.189526518</v>
+        <v>0.189110501</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185274611</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185276895</v>
+        <v>0.185295496</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185290153</v>
+        <v>0.185294016</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185292951</v>
+        <v>0.185277307</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185282523</v>
+        <v>0.18528159</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185293538</v>
+        <v>0.185292545</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003986799</v>
+        <v>-0.004631899</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.005360371</v>
+        <v>0.004773709</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001959121</v>
+        <v>0.001389088</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>302.000337721</v>
+        <v>301.999587044</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.003124256</v>
+        <v>0.002369067</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.002092481</v>
+        <v>-0.002785396</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.006109544</v>
+        <v>0.007414663</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.007189902</v>
+        <v>302.002181462</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.001172659</v>
+        <v>0.0060292</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.003371684</v>
+        <v>-0.001921931</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.000507115</v>
+        <v>-0.001039757</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.001206204</v>
+        <v>-0.000211803</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002109312</v>
+        <v>-0.003493535</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.015091283</v>
+        <v>302.013290673</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.002032197</v>
+        <v>-0.003819309</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.003124236</v>
+        <v>0.001474076</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.001430277</v>
+        <v>0.001799901</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.021198443</v>
+        <v>302.014993786</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.004694966</v>
+        <v>-0.00100984</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.007824104</v>
+        <v>0.001423144</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8156,16 +8156,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.06387691199999999</v>
+        <v>0.063863806</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.295354596</v>
+        <v>-0.295382872</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.10662401</v>
+        <v>0.106577153</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.091121643</v>
+        <v>0.091098682</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>43050</v>
+        <v>43100</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,350원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1977921026407574</v>
+        <v>0.1978042513431441</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683227007507426</v>
+        <v>0.16832298733804</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999029521942507</v>
+        <v>0.9998835290692033</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03404456940860105</v>
+        <v>0.03404494335299118</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37748,7 +37748,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39888,7 +39888,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 152552억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 152550억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159017억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 159016억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164214억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164216억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171275억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171283억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181401억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181419억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 152552억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 152550억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159017억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 159016억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164214억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164216억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171275억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171283억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181401억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181419억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6316,13 +6316,13 @@
         <v>0.193702802</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.173409507</v>
+        <v>0.173440556</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.16244384</v>
+        <v>0.162504967</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.189110501</v>
+        <v>0.189244361</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6633,13 +6633,13 @@
         <v>0.185294016</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185277307</v>
+        <v>0.185272405</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.18528159</v>
+        <v>0.185271848</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185292545</v>
+        <v>0.185271689</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.004631899</v>
+        <v>-0.004451968</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004773709</v>
+        <v>0.004939816</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001389088</v>
+        <v>0.001551894</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.999587044</v>
+        <v>301.99979655</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.002369067</v>
+        <v>0.002574487</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.002785396</v>
+        <v>-0.002594627</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.007414663</v>
+        <v>0.007601392</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.002181462</v>
+        <v>302.012351992</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.0060292</v>
+        <v>-0.00373737</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001921931</v>
+        <v>-0.011632822</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.001039757</v>
+        <v>-0.000859847</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.000211803</v>
+        <v>-4.5715e-05</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003493535</v>
+        <v>-0.003330748</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.013290673</v>
+        <v>302.013500155</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.003819309</v>
+        <v>-0.003613913</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.001474076</v>
+        <v>0.001664823</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.001799901</v>
+        <v>0.001986607</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.014993786</v>
+        <v>302.015164297</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.00100984</v>
+        <v>-0.010776438</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.001423144</v>
+        <v>0.00171222</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8156,16 +8156,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.063863806</v>
+        <v>0.0638507</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.295382872</v>
+        <v>-0.295374192</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.106577153</v>
+        <v>0.106594636</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.091098682</v>
+        <v>0.09109724299999999</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1978042513431441</v>
+        <v>0.197801171047714</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.16832298733804</v>
+        <v>0.1683224160695287</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03404494335299118</v>
+        <v>0.0340449539412188</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 152550억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 152543억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159016억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 159008억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164216억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164207억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171283억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171274억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181419억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181417억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 152550억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 152543억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159016억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 159008억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164216억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164207억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171283억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171274억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181419억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181417억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>43100</v>
+        <v>42900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43400</v>
+        <v>43290</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6309,20 +6309,20 @@
         <v>0.1819167</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.19399049</v>
+        <v>0.193910577</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.193702802</v>
+        <v>0.193661536</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.173440556</v>
+        <v>0.173378458</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.162504967</v>
+        <v>0.16244384</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.189244361</v>
+        <v>0.189290495</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185274611</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185295496</v>
+        <v>0.185274431</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185294016</v>
+        <v>0.185265851</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185272405</v>
+        <v>0.18528221</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185271848</v>
+        <v>0.18528159</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185271689</v>
+        <v>0.185276902</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.004451968</v>
+        <v>-0.004617434</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004939816</v>
+        <v>0.004789052</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001551894</v>
+        <v>0.001405239</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.99979655</v>
+        <v>301.99960399</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.002574487</v>
+        <v>0.002381389</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.002594627</v>
+        <v>-0.000794108</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.007601392</v>
+        <v>-0.010661274</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.012351992</v>
+        <v>302.012128454</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.00373737</v>
+        <v>0.006039885</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.011632822</v>
+        <v>-0.011910174</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.000859847</v>
+        <v>-0.000124158</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-4.5715e-05</v>
+        <v>0.000634295</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003330748</v>
+        <v>-0.002663773</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.013500155</v>
+        <v>302.014356809</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.003613913</v>
+        <v>-0.002775793</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.001664823</v>
+        <v>-0.005577289</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.001986607</v>
+        <v>0.00466036</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.015164297</v>
+        <v>302.006138497</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.010776438</v>
+        <v>0.000173789</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.00171222</v>
+        <v>0.002543839</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8152,20 +8152,20 @@
         <v>0.081357268</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.069838199</v>
+        <v>0.069824178</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.0638507</v>
+        <v>0.063864643</v>
       </c>
       <c r="AL34" s="24" t="n">
         <v>-0.295374192</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.106594636</v>
+        <v>0.106577153</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09109724299999999</v>
+        <v>0.091098682</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>43100</v>
+        <v>42900</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,350원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,150원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.197801171047714</v>
+        <v>0.1978042513431441</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683224160695287</v>
+        <v>0.1683267315309772</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9998835290692033</v>
+        <v>0.9999029371226682</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0340449539412188</v>
+        <v>0.03404503651116909</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37748,7 +37748,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39888,7 +39888,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.71</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="32">
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -681,37 +681,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 147342억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 148126억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 152543억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155049억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 159008억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164207억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167668억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171274억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173658억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181417억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181569억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1548,37 +1548,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 147342억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 148126억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 152543억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155049억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 159008억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164207억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167668억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171274억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173658억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181417억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181569억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1920,25 +1920,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 763억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 764억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 812억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 814억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 572억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 575억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 633억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 637억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1980,25 +1980,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 763억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 764억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 812억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 814억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 572억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 575억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 633억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 637억 × 3.40%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -6306,23 +6306,23 @@
         <v>0.344572968</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.1819167</v>
+        <v>0.188238269</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.193910577</v>
+        <v>0.213529388</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.193661536</v>
+        <v>0.218586225</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.173378458</v>
+        <v>0.198093582</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.16244384</v>
+        <v>0.17234146</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.189290495</v>
+        <v>0.171051332</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6620,26 +6620,26 @@
         <v>0.185270283</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.185274611</v>
+        <v>0.185292151</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185274431</v>
+        <v>0.185275427</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185265851</v>
+        <v>0.185269218</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.18528221</v>
+        <v>0.185295566</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.18528159</v>
+        <v>0.185281228</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185276902</v>
+        <v>0.185289321</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.004617434</v>
+        <v>-0.005706675</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004789052</v>
+        <v>0.003619985</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001405239</v>
+        <v>0.000167777</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.99960399</v>
+        <v>301.998327317</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.002381389</v>
+        <v>0.00620781</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.000794108</v>
+        <v>-9.146e-06</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.010661274</v>
+        <v>-0.006510426</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.012128454</v>
+        <v>302.011236343</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.006039885</v>
+        <v>0.002537426</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.011910174</v>
+        <v>-0.008005688</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.000124158</v>
+        <v>-0.001178828</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.000634295</v>
+        <v>-0.000502883</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002663773</v>
+        <v>-0.003869997</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.014356809</v>
+        <v>302.013120388</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.002775793</v>
+        <v>0.001064658</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.005577289</v>
+        <v>-0.004826136</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.00466036</v>
+        <v>-0.001240101</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.006138497</v>
+        <v>302.015176697</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.000173789</v>
+        <v>-0.003361488</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.002543839</v>
+        <v>0.00648362</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8149,23 +8149,23 @@
         <v>-0.272795431</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.081357268</v>
+        <v>0.08175147100000001</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.069824178</v>
+        <v>0.070821887</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.063864643</v>
+        <v>0.064972972</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.295374192</v>
+        <v>-0.293221901</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.106577153</v>
+        <v>0.107413011</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.091098682</v>
+        <v>0.09065071299999999</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1978042513431441</v>
+        <v>0.1978025374356756</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683267315309772</v>
+        <v>0.1683271838581839</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999029371226682</v>
+        <v>0.9999036794451934</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03404503651116909</v>
+        <v>0.03403738276678182</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12378,9 +12378,33 @@
       <c r="S34" s="18" t="n">
         <v>87.94</v>
       </c>
-      <c r="U34" s="9" t="n"/>
-      <c r="Z34" s="9" t="n"/>
-      <c r="AB34" s="5" t="n"/>
+      <c r="T34" s="18" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="U34" s="37" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="V34" s="18" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="W34" s="18" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="X34" s="18" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Y34" s="18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z34" s="37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA34" s="18" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="AB34" s="19" t="n">
+        <v>81.01000000000001</v>
+      </c>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
@@ -12710,9 +12734,33 @@
       <c r="S38" s="18" t="n">
         <v>40.57</v>
       </c>
-      <c r="U38" s="9" t="n"/>
-      <c r="Z38" s="9" t="n"/>
-      <c r="AB38" s="5" t="n"/>
+      <c r="T38" s="18" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="U38" s="37" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="V38" s="18" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="W38" s="18" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="X38" s="18" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Y38" s="18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z38" s="37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA38" s="18" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="AB38" s="19" t="n">
+        <v>81.01000000000001</v>
+      </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
@@ -12781,13 +12829,32 @@
       <c r="S39" s="18" t="n">
         <v>40.57</v>
       </c>
-      <c r="U39" s="9" t="n"/>
-      <c r="Z39" s="9" t="n"/>
+      <c r="T39" s="18" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="U39" s="37" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="V39" s="18" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="W39" s="18" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="X39" s="18" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Y39" s="18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z39" s="37" t="n">
+        <v>1.1</v>
+      </c>
       <c r="AA39" s="18" t="n">
-        <v>4398.85</v>
+        <v>4416.72</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>3051.45</v>
+        <v>3132.46</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -18300,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20819,7 +20886,7 @@
         <v>18.97</v>
       </c>
       <c r="AB30" s="19" t="n">
-        <v>34.57</v>
+        <v>115.58</v>
       </c>
       <c r="AC30" s="10" t="n"/>
       <c r="AD30" s="10" t="n"/>
@@ -21097,7 +21164,9 @@
       <c r="Z33" s="37" t="n">
         <v>1.1</v>
       </c>
-      <c r="AB33" s="5" t="n"/>
+      <c r="AB33" s="19" t="n">
+        <v>81.01000000000001</v>
+      </c>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
@@ -21191,7 +21260,7 @@
         <v>4398.85</v>
       </c>
       <c r="AB34" s="19" t="n">
-        <v>3051.45</v>
+        <v>3132.46</v>
       </c>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 155049억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155047억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162349억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167668억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167708억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 173658억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173718억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181569억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181651억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 155049억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155047억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162349억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167668억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167708억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 173658억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173718억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181569억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181651억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42900</v>
+        <v>42950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43290</v>
+        <v>43300</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6313,16 +6313,16 @@
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.218586225</v>
+        <v>0.218710024</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.198093582</v>
+        <v>0.198404074</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.17234146</v>
+        <v>0.17276707</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.171051332</v>
+        <v>0.17157815</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6630,16 +6630,16 @@
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185269218</v>
+        <v>0.185284258</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185295566</v>
+        <v>0.185273467</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185281228</v>
+        <v>0.185291754</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185289321</v>
+        <v>0.185290315</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.005706675</v>
+        <v>-0.005567641</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.003619985</v>
+        <v>0.00374427</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.000167777</v>
+        <v>0.000287313</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.998327317</v>
+        <v>301.998488994</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.00620781</v>
+        <v>0.006376066</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-9.146e-06</v>
+        <v>0.000144971</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.006510426</v>
+        <v>-0.008339493999999999</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.011236343</v>
+        <v>302.009455289</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.002537426</v>
+        <v>0.006939519</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.008005688</v>
+        <v>-0.003552123</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.001178828</v>
+        <v>0.0007493689999999999</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.000502883</v>
+        <v>0.001270828</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003869997</v>
+        <v>-0.002135079</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.013120388</v>
+        <v>302.015365189</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.001064658</v>
+        <v>0.003290522</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.004826136</v>
+        <v>-0.002744898</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.001240101</v>
+        <v>0.008822557</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.015176697</v>
+        <v>302.005819446</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.003361488</v>
+        <v>0.013399169</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.00648362</v>
+        <v>0.003140433</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8159,13 +8159,13 @@
         <v>0.064972972</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.293221901</v>
+        <v>-0.293197321</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.107413011</v>
+        <v>0.107426664</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09065071299999999</v>
+        <v>0.090693548</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>42900</v>
+        <v>42950</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,150원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,350원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1978025374356756</v>
+        <v>0.1977996507872738</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683271838581839</v>
+        <v>0.168323249783924</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999036794451934</v>
+        <v>0.9999422143462516</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03403738276678182</v>
+        <v>0.03403720218194575</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.66</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="32">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 155047억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155044억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162349억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162338억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167708억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167688억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 173718억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173690억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181651억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181617억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 155047억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155044억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162349억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162338억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167708억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167688억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 173718억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173690억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181651억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181617억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6309,20 +6309,20 @@
         <v>0.188238269</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.213529388</v>
+        <v>0.213489431</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.218710024</v>
+        <v>0.218627491</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.198404074</v>
+        <v>0.198248828</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.17276707</v>
+        <v>0.172554265</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.17157815</v>
+        <v>0.171419164</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185292151</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185275427</v>
+        <v>0.185281528</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185284258</v>
+        <v>0.185296807</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185273467</v>
+        <v>0.185297471</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185291754</v>
+        <v>0.185299456</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185290315</v>
+        <v>0.185293456</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.005567641</v>
+        <v>-0.005187052</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.00374427</v>
+        <v>0.004097485</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.000287313</v>
+        <v>0.000634555</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.998488994</v>
+        <v>301.998932235</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.006376066</v>
+        <v>0.006808708</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.000144971</v>
+        <v>0.000552362</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.008339493999999999</v>
+        <v>0.00206197</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.009455289</v>
+        <v>302.009965837</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.006939519</v>
+        <v>0.009341812</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.003552123</v>
+        <v>-0.001248452</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.0007493689999999999</v>
+        <v>-0.00065891</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.001270828</v>
+        <v>-2.5113e-05</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002135079</v>
+        <v>-0.003402952</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.015365189</v>
+        <v>302.01372565</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.003290522</v>
+        <v>0.001665894</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.002744898</v>
+        <v>0.005735689</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.008822557</v>
+        <v>-0.002668167</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.005819446</v>
+        <v>302.013905819</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.013399169</v>
+        <v>0.013441732</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.003140433</v>
+        <v>0.003239667</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8159,13 +8159,13 @@
         <v>0.064972972</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.293197321</v>
+        <v>-0.293209611</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.107426664</v>
+        <v>0.107411143</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.090693548</v>
+        <v>0.09068069400000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1977996507872738</v>
+        <v>0.1977933677411379</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.168323249783924</v>
+        <v>0.1683249492346266</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999422143462516</v>
+        <v>0.9999036868667412</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03403720218194575</v>
+        <v>0.03403731125696816</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42950</v>
+        <v>42550</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>39600</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>42500</v>
+        <v>42350</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43300</v>
+        <v>43175</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>42950</v>
+        <v>42550</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39957,7 +39957,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.67</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="32">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 155044억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155037억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162338억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162295억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167688억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167608억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 173690억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173572억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181617억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181469억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 155044억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155037억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162338억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162295억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167688억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167608억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 173690억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173572억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181617억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181469억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42550</v>
+        <v>42850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>39600</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>42350</v>
+        <v>41550</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43175</v>
+        <v>43064.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6309,20 +6309,20 @@
         <v>0.188238269</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.213489431</v>
+        <v>0.213449475</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.218627491</v>
+        <v>0.218297363</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.198248828</v>
+        <v>0.197658894</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.172554265</v>
+        <v>0.171763848</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.171419164</v>
+        <v>0.170502815</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185292151</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185281528</v>
+        <v>0.185287629</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185296807</v>
+        <v>0.185279274</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185297471</v>
+        <v>0.185285044</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185299456</v>
+        <v>0.185294728</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185293456</v>
+        <v>0.185275832</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.005187052</v>
+        <v>-0.006318019</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004097485</v>
+        <v>0.003067048</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.000634555</v>
+        <v>-0.000367767</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.998932235</v>
+        <v>301.997616076</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.006808708</v>
+        <v>0.005481836</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.000552362</v>
+        <v>-0.0006794630000000001</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.00206197</v>
+        <v>-0.005184268</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.009965837</v>
+        <v>302.006182518</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.009341812</v>
+        <v>0.007348209</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001248452</v>
+        <v>-0.001355649</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.00065891</v>
+        <v>-0.001790888</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-2.5113e-05</v>
+        <v>-0.001056482</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003402952</v>
+        <v>-0.00440619</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.01372565</v>
+        <v>302.012408314</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.001665894</v>
+        <v>0.000337861</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.005735689</v>
+        <v>0.004502776</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.002668167</v>
+        <v>8.6073e-05</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.013905819</v>
+        <v>302.010124235</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.013441732</v>
+        <v>0.001450698</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.003239667</v>
+        <v>-0.006864083</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8156,16 +8156,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.064972972</v>
+        <v>0.064946794</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.293209611</v>
+        <v>-0.29325369</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.107411143</v>
+        <v>0.107368311</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09068069400000001</v>
+        <v>0.09062927</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>42550</v>
+        <v>42850</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 43,350원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 42,900원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1977933677411379</v>
+        <v>0.1978144272531957</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683249492346266</v>
+        <v>0.1683248569612206</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999036868667412</v>
+        <v>0.999903662742529</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03403731125696816</v>
+        <v>0.0340378775054</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39957,7 +39957,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.57</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="32">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 155037억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155036억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162295억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167608억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167680억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 173572억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173680억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181469억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181612억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 155037억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155036억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162295억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167608억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167680억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 173572억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173680억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181469억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181612억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42850</v>
+        <v>42600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43064.3</v>
+        <v>43037.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6313,16 +6313,16 @@
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.218297363</v>
+        <v>0.218586225</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.197658894</v>
+        <v>0.19818673</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.171763848</v>
+        <v>0.172493464</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.170502815</v>
+        <v>0.171424808</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6630,16 +6630,16 @@
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185279274</v>
+        <v>0.185269218</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185285044</v>
+        <v>0.185281161</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185294728</v>
+        <v>0.185283136</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185275832</v>
+        <v>0.185270555</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.006318019</v>
+        <v>-0.005522304</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.003067048</v>
+        <v>0.003790992</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.000367767</v>
+        <v>0.000335834</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.997616076</v>
+        <v>301.998542033</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.005481836</v>
+        <v>0.006417621</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.0006794630000000001</v>
+        <v>0.0001884</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005184268</v>
+        <v>-0.006315966</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.006182518</v>
+        <v>302.011415639</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.007348209</v>
+        <v>0.000798302</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001355649</v>
+        <v>-0.009759512999999999</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.001790888</v>
+        <v>-9.9972e-05</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.001056482</v>
+        <v>0.000492748</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.00440619</v>
+        <v>-0.002894336</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.012408314</v>
+        <v>302.014376554</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.000337861</v>
+        <v>0.002303162</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.004502776</v>
+        <v>0.006334868</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>8.6073e-05</v>
+        <v>-9.964800000000001e-05</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.010124235</v>
+        <v>302.006568002</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.001450698</v>
+        <v>0.006078624</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.006864083</v>
+        <v>-0.004168617</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8156,16 +8156,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.064946794</v>
+        <v>0.064959883</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.29325369</v>
+        <v>-0.293213215</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.107368311</v>
+        <v>0.107413011</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09062927</v>
+        <v>0.09068211800000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>42850</v>
+        <v>42600</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 42,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 42,450원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1978144272531957</v>
+        <v>0.197799480776363</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683248569612206</v>
+        <v>0.1683286936404429</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.999903662742529</v>
+        <v>0.9999229450405502</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0340378775054</v>
+        <v>0.03403743078910799</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39957,7 +39957,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.65</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="32">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 155036억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155134억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162466억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167680억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167792억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 173680억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173721억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181612억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181448억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 155036억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155134억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162330억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162466억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167680억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167792억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 173680억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173721억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181612억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181448억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42600</v>
+        <v>45000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5959,7 +5959,7 @@
         <v>47400</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>44350</v>
+        <v>45050</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>39600</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>41550</v>
+        <v>40900</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43037.5</v>
+        <v>43227.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6309,20 +6309,20 @@
         <v>0.188238269</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.213449475</v>
+        <v>0.214208655</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.218586225</v>
+        <v>0.219617876</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.19818673</v>
+        <v>0.198994008</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.172493464</v>
+        <v>0.17276707</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.171424808</v>
+        <v>0.169606424</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185292151</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185287629</v>
+        <v>0.185270502</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185269218</v>
+        <v>0.185281678</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185281161</v>
+        <v>0.185285892</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185283136</v>
+        <v>0.185291754</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185270555</v>
+        <v>0.185273761</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.005522304</v>
+        <v>-0.006809051</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.003790992</v>
+        <v>0.00257756</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.000335834</v>
+        <v>-0.000867805</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.998542033</v>
+        <v>301.997042477</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.006417621</v>
+        <v>0.004996225</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.0001884</v>
+        <v>-0.007101557</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.006315966</v>
+        <v>0.002650808</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.011415639</v>
+        <v>302.010318621</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.000798302</v>
+        <v>-0.004060003</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.009759512999999999</v>
+        <v>-0.008576627</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-9.9972e-05</v>
+        <v>-0.002280323</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.000492748</v>
+        <v>-0.001544493</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002894336</v>
+        <v>-0.004904779</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.014376554</v>
+        <v>302.011836575</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.002303162</v>
+        <v>-0.000145919</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.006334868</v>
+        <v>-0.001919918</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-9.964800000000001e-05</v>
+        <v>-0.002081819</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.006568002</v>
+        <v>302.014256263</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.006078624</v>
+        <v>3.985e-05</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.004168617</v>
+        <v>-0.004082455</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8152,20 +8152,20 @@
         <v>0.08175147100000001</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.070821887</v>
+        <v>0.070863935</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.064959883</v>
+        <v>0.065009685</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.293213215</v>
+        <v>-0.293151123</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.107413011</v>
+        <v>0.107429108</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09068211800000001</v>
+        <v>0.090586536</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>42600</v>
+        <v>45000</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 42,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 41,550원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.197799480776363</v>
+        <v>0.1978183278997543</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683286936404429</v>
+        <v>0.1683263324457775</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999229450405502</v>
+        <v>0.9999036961420675</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03403743078910799</v>
+        <v>0.03403616910088912</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39957,7 +39957,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.58</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="32">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/065710_model.xlsx
+++ b/argus/kship/models/065710_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 155134억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 155198억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162466억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162573억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167792억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167893억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 173721억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 173779억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 181448억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 181372억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1554,31 +1554,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 155134억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 155198억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162466억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162573억 × 비례계수 0.0083 × 계절비중 Q1 0.219(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167792억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167893억 × 비례계수 0.0083 × 계절비중 Q2 0.277(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 173721억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 173779억 × 비례계수 0.0083 × 계절비중 Q3 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 181448억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 181372억 × 비례계수 0.0083 × 계절비중 Q4 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.92, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>43700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>45000</v>
+        <v>44650</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5959,7 +5959,7 @@
         <v>47400</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>45050</v>
+        <v>46400</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>44098.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43227.3</v>
+        <v>43693.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6309,20 +6309,20 @@
         <v>0.188238269</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.214208655</v>
+        <v>0.214688137</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.219617876</v>
+        <v>0.220401931</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.198994008</v>
+        <v>0.199708138</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.17276707</v>
+        <v>0.173162279</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.169606424</v>
+        <v>0.168651316</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6623,23 +6623,23 @@
         <v>0.185292151</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.185270502</v>
+        <v>0.185296053</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.185281678</v>
+        <v>0.185297897</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.185285892</v>
+        <v>0.185279122</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.185291754</v>
+        <v>0.185281161</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.185273761</v>
+        <v>0.185295691</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7664,36 +7664,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.006809051</v>
+        <v>-0.003520228</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.00257756</v>
+        <v>0.005795889</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.000867805</v>
+        <v>0.002388675</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>301.997042477</v>
+        <v>302.000881225</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.004996225</v>
+        <v>0.008377992000000001</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.007101557</v>
+        <v>0.000299288</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.002650808</v>
+        <v>0.008260910999999999</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>302.010318621</v>
+        <v>302.00679813</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.004060003</v>
+        <v>0.006095802</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.008576627</v>
+        <v>-0.000437351</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7792,36 +7792,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002280323</v>
+        <v>0.001008958</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.001544493</v>
+        <v>0.001674241</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.004904779</v>
+        <v>-0.001647914</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>302.011836575</v>
+        <v>302.015675857</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.000145919</v>
+        <v>0.003236413</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.001919918</v>
+        <v>0.005479124</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.002081819</v>
+        <v>0.003525675</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>302.014256263</v>
+        <v>302.01073331</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>3.985e-05</v>
+        <v>0.010194737</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.004082455</v>
+        <v>0.004058918</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8152,20 +8152,20 @@
         <v>0.08175147100000001</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.070863935</v>
+        <v>0.070891966</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.065009685</v>
+        <v>0.065047248</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.293151123</v>
+        <v>-0.293096245</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.107429108</v>
+        <v>0.107448935</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.090586536</v>
+        <v>0.090540922</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>45000</v>
+        <v>44650</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 41,550원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 44,050원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1978183278997543</v>
+        <v>0.1977847123524687</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1683263324457775</v>
+        <v>0.1683271172333166</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.9999036961420675</v>
+        <v>0.9999037128331535</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03403616910088912</v>
+        <v>0.03404481942551206</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39957,7 +39957,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.23</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="32">
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="33">
